--- a/data/mercichor_2025.xlsx
+++ b/data/mercichor_2025.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30611"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,16 +10,27 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A42D567-7007-4560-A26F-8051D1BC59F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заявка" sheetId="3" r:id="rId1"/>
     <sheet name="Стартовый протокол" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -374,9 +385,6 @@
   </si>
   <si>
     <t>Кирпий Максим</t>
-  </si>
-  <si>
-    <t>Шемянский Богдар</t>
   </si>
   <si>
     <t>Амелькин Владислав</t>
@@ -1717,19 +1725,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H332"/>
-  <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="11" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" style="11" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="3.359375" customWidth="1"/>
+    <col min="2" max="2" width="22.734375" customWidth="1"/>
+    <col min="3" max="3" width="9.55078125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14.2578125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="11.56640625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="18.4296875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16">
         <v>45717</v>
       </c>
@@ -1743,9 +1751,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -1755,7 +1763,7 @@
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
     </row>
-    <row r="3" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -1765,7 +1773,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>57</v>
       </c>
@@ -1777,7 +1785,7 @@
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>0</v>
       </c>
@@ -1794,16 +1802,16 @@
         <v>59</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>1</v>
       </c>
@@ -1820,7 +1828,7 @@
         <v>63</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G6" s="10">
         <v>3</v>
@@ -1829,7 +1837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>2</v>
       </c>
@@ -1846,16 +1854,16 @@
         <v>63</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -1872,16 +1880,16 @@
         <v>63</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <v>4</v>
       </c>
@@ -1898,16 +1906,16 @@
         <v>63</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>5</v>
       </c>
@@ -1924,16 +1932,16 @@
         <v>63</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>6</v>
       </c>
@@ -1950,16 +1958,16 @@
         <v>63</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>7</v>
       </c>
@@ -1976,16 +1984,16 @@
         <v>63</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <v>8</v>
       </c>
@@ -2002,16 +2010,16 @@
         <v>63</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <v>9</v>
       </c>
@@ -2028,16 +2036,16 @@
         <v>63</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>10</v>
       </c>
@@ -2054,16 +2062,16 @@
         <v>63</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10"/>
     </row>
-    <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>0</v>
       </c>
@@ -2080,16 +2088,16 @@
         <v>59</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
         <v>1</v>
       </c>
@@ -2106,7 +2114,7 @@
         <v>63</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="10">
         <v>3</v>
@@ -2115,7 +2123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <v>2</v>
       </c>
@@ -2132,7 +2140,7 @@
         <v>63</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="10">
         <v>3</v>
@@ -2141,7 +2149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
         <v>3</v>
       </c>
@@ -2158,7 +2166,7 @@
         <v>63</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G20" s="10">
         <v>3</v>
@@ -2167,7 +2175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="11">
         <v>4</v>
       </c>
@@ -2184,16 +2192,16 @@
         <v>63</v>
       </c>
       <c r="F21" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>398</v>
-      </c>
       <c r="H21" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="11">
         <v>5</v>
       </c>
@@ -2210,16 +2218,16 @@
         <v>63</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
         <v>6</v>
       </c>
@@ -2236,13 +2244,13 @@
         <v>63</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="11">
         <v>7</v>
       </c>
@@ -2259,13 +2267,13 @@
         <v>63</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="11">
         <v>8</v>
       </c>
@@ -2282,16 +2290,16 @@
         <v>63</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="11"/>
     </row>
-    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
         <v>0</v>
       </c>
@@ -2308,16 +2316,16 @@
         <v>59</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1</v>
       </c>
@@ -2334,16 +2342,16 @@
         <v>63</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2</v>
       </c>
@@ -2360,16 +2368,16 @@
         <v>63</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2386,16 +2394,16 @@
         <v>63</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2412,16 +2420,16 @@
         <v>63</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2438,16 +2446,16 @@
         <v>63</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>6</v>
       </c>
@@ -2464,13 +2472,13 @@
         <v>63</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>7</v>
       </c>
@@ -2487,13 +2495,13 @@
         <v>63</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H34" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>8</v>
       </c>
@@ -2510,18 +2518,18 @@
         <v>63</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C36" s="11">
         <v>2014</v>
@@ -2533,13 +2541,13 @@
         <v>63</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>10</v>
       </c>
@@ -2556,13 +2564,13 @@
         <v>63</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>11</v>
       </c>
@@ -2579,13 +2587,13 @@
         <v>63</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>12</v>
       </c>
@@ -2602,13 +2610,13 @@
         <v>63</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>13</v>
       </c>
@@ -2625,13 +2633,13 @@
         <v>63</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>14</v>
       </c>
@@ -2648,13 +2656,13 @@
         <v>63</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>15</v>
       </c>
@@ -2671,13 +2679,13 @@
         <v>63</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H42" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
         <v>0</v>
       </c>
@@ -2694,16 +2702,16 @@
         <v>59</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1</v>
       </c>
@@ -2720,7 +2728,7 @@
         <v>63</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G45" s="10">
         <v>3</v>
@@ -2729,7 +2737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>2</v>
       </c>
@@ -2746,16 +2754,16 @@
         <v>63</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>3</v>
       </c>
@@ -2772,16 +2780,16 @@
         <v>63</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>4</v>
       </c>
@@ -2798,16 +2806,16 @@
         <v>63</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H48" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>5</v>
       </c>
@@ -2824,16 +2832,16 @@
         <v>63</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H49" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>6</v>
       </c>
@@ -2850,16 +2858,16 @@
         <v>63</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H50" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>7</v>
       </c>
@@ -2876,16 +2884,16 @@
         <v>63</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H51" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>8</v>
       </c>
@@ -2902,16 +2910,16 @@
         <v>63</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H52" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>9</v>
       </c>
@@ -2928,16 +2936,16 @@
         <v>63</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H53" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>10</v>
       </c>
@@ -2954,13 +2962,13 @@
         <v>63</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H54" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>11</v>
       </c>
@@ -2977,13 +2985,13 @@
         <v>63</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H55" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>12</v>
       </c>
@@ -3000,13 +3008,13 @@
         <v>63</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H56" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>13</v>
       </c>
@@ -3023,13 +3031,13 @@
         <v>63</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H57" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>14</v>
       </c>
@@ -3046,13 +3054,13 @@
         <v>63</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H58" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="14" t="s">
         <v>106</v>
       </c>
@@ -3064,7 +3072,7 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
     </row>
-    <row r="61" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9" t="s">
         <v>0</v>
       </c>
@@ -3081,16 +3089,16 @@
         <v>59</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="10">
         <v>1</v>
       </c>
@@ -3107,16 +3115,16 @@
         <v>63</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="10">
         <v>2</v>
       </c>
@@ -3133,16 +3141,16 @@
         <v>63</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H63" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="10">
         <v>3</v>
       </c>
@@ -3159,16 +3167,16 @@
         <v>63</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="11">
         <v>4</v>
       </c>
@@ -3185,16 +3193,16 @@
         <v>63</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H65" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="11">
         <v>5</v>
       </c>
@@ -3211,13 +3219,13 @@
         <v>63</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H66" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="11">
         <v>6</v>
       </c>
@@ -3234,13 +3242,13 @@
         <v>63</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H67" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="11">
         <v>7</v>
       </c>
@@ -3257,13 +3265,13 @@
         <v>63</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H68" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="11">
         <v>8</v>
       </c>
@@ -3280,13 +3288,13 @@
         <v>63</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H69" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="11">
         <v>9</v>
       </c>
@@ -3303,13 +3311,13 @@
         <v>63</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H70" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="11">
         <v>10</v>
       </c>
@@ -3326,16 +3334,16 @@
         <v>63</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H71" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="11"/>
     </row>
-    <row r="73" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
         <v>0</v>
       </c>
@@ -3352,16 +3360,16 @@
         <v>59</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="10">
         <v>1</v>
       </c>
@@ -3378,21 +3386,21 @@
         <v>63</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H74" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="10">
         <v>2</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C75" s="10">
         <v>2015</v>
@@ -3404,16 +3412,16 @@
         <v>63</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="10">
         <v>3</v>
       </c>
@@ -3430,16 +3438,16 @@
         <v>63</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="10">
         <v>4</v>
       </c>
@@ -3456,16 +3464,16 @@
         <v>63</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H77" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="10">
         <v>5</v>
       </c>
@@ -3482,16 +3490,16 @@
         <v>63</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H78" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="10">
         <v>6</v>
       </c>
@@ -3508,13 +3516,13 @@
         <v>63</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H79" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="10">
         <v>7</v>
       </c>
@@ -3531,13 +3539,13 @@
         <v>63</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H80" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -3554,13 +3562,13 @@
         <v>63</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H81" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="10">
         <v>9</v>
       </c>
@@ -3577,13 +3585,13 @@
         <v>63</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H82" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -3600,13 +3608,13 @@
         <v>63</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H83" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="10">
         <v>11</v>
       </c>
@@ -3623,13 +3631,13 @@
         <v>63</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H84" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="10">
         <v>12</v>
       </c>
@@ -3646,13 +3654,13 @@
         <v>63</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H85" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="10">
         <v>13</v>
       </c>
@@ -3669,13 +3677,13 @@
         <v>63</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H86" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="10">
         <v>14</v>
       </c>
@@ -3692,13 +3700,13 @@
         <v>63</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H87" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="10">
         <v>15</v>
       </c>
@@ -3715,13 +3723,13 @@
         <v>63</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H88" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="10">
         <v>16</v>
       </c>
@@ -3738,13 +3746,13 @@
         <v>63</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H89" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="10">
         <v>17</v>
       </c>
@@ -3761,13 +3769,13 @@
         <v>63</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H90" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="10">
         <v>18</v>
       </c>
@@ -3784,13 +3792,13 @@
         <v>63</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H91" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="10">
         <v>19</v>
       </c>
@@ -3807,13 +3815,13 @@
         <v>63</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H92" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="10">
         <v>20</v>
       </c>
@@ -3830,13 +3838,13 @@
         <v>63</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H93" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="10">
         <v>21</v>
       </c>
@@ -3853,13 +3861,13 @@
         <v>63</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H94" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="10">
         <v>22</v>
       </c>
@@ -3876,13 +3884,13 @@
         <v>63</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H95" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="10">
         <v>23</v>
       </c>
@@ -3899,13 +3907,13 @@
         <v>63</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H96" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <v>24</v>
       </c>
@@ -3922,13 +3930,13 @@
         <v>63</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H97" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="10">
         <v>25</v>
       </c>
@@ -3945,13 +3953,13 @@
         <v>63</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H98" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="10">
         <v>26</v>
       </c>
@@ -3968,13 +3976,13 @@
         <v>63</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H99" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="10">
         <v>27</v>
       </c>
@@ -3991,13 +3999,13 @@
         <v>63</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H100" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="10">
         <v>28</v>
       </c>
@@ -4014,16 +4022,16 @@
         <v>63</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H101" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="11"/>
     </row>
-    <row r="103" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="14" t="s">
         <v>106</v>
       </c>
@@ -4035,7 +4043,7 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
     </row>
-    <row r="104" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="9" t="s">
         <v>0</v>
       </c>
@@ -4052,16 +4060,16 @@
         <v>59</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H104" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="11">
         <v>1</v>
       </c>
@@ -4078,16 +4086,16 @@
         <v>63</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="11">
         <v>2</v>
       </c>
@@ -4104,16 +4112,16 @@
         <v>63</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H106" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="11">
         <v>3</v>
       </c>
@@ -4130,16 +4138,16 @@
         <v>63</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="11">
         <v>4</v>
       </c>
@@ -4156,16 +4164,16 @@
         <v>63</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H108" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="11">
         <v>5</v>
       </c>
@@ -4182,16 +4190,16 @@
         <v>63</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H109" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="11">
         <v>6</v>
       </c>
@@ -4208,16 +4216,16 @@
         <v>63</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H110" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="11">
         <v>7</v>
       </c>
@@ -4234,16 +4242,16 @@
         <v>63</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H111" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="11">
         <v>8</v>
       </c>
@@ -4260,16 +4268,16 @@
         <v>63</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H112" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="11">
         <v>9</v>
       </c>
@@ -4286,16 +4294,16 @@
         <v>63</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H113" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="11">
         <v>10</v>
       </c>
@@ -4312,16 +4320,16 @@
         <v>63</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H114" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="11"/>
     </row>
-    <row r="116" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="9" t="s">
         <v>0</v>
       </c>
@@ -4338,16 +4346,16 @@
         <v>59</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H116" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="11">
         <v>1</v>
       </c>
@@ -4364,7 +4372,7 @@
         <v>63</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G117" s="10">
         <v>2</v>
@@ -4373,7 +4381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="11">
         <v>2</v>
       </c>
@@ -4390,7 +4398,7 @@
         <v>63</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G118" s="10">
         <v>3</v>
@@ -4399,7 +4407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="11">
         <v>3</v>
       </c>
@@ -4416,7 +4424,7 @@
         <v>63</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G119" s="10">
         <v>3</v>
@@ -4425,7 +4433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="11">
         <v>4</v>
       </c>
@@ -4442,16 +4450,16 @@
         <v>63</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G120" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H120" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="11">
         <v>5</v>
       </c>
@@ -4468,16 +4476,16 @@
         <v>63</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H121" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="11">
         <v>6</v>
       </c>
@@ -4494,13 +4502,13 @@
         <v>63</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H122" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="11">
         <v>7</v>
       </c>
@@ -4517,13 +4525,13 @@
         <v>63</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H123" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="11">
         <v>8</v>
       </c>
@@ -4540,16 +4548,16 @@
         <v>63</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H124" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="11"/>
     </row>
-    <row r="126" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="9" t="s">
         <v>0</v>
       </c>
@@ -4566,16 +4574,16 @@
         <v>59</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H126" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>1</v>
       </c>
@@ -4592,16 +4600,16 @@
         <v>63</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>2</v>
       </c>
@@ -4618,16 +4626,16 @@
         <v>63</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H128" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>3</v>
       </c>
@@ -4644,16 +4652,16 @@
         <v>63</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G129" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>4</v>
       </c>
@@ -4670,16 +4678,16 @@
         <v>63</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G130" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H130" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>5</v>
       </c>
@@ -4696,16 +4704,16 @@
         <v>63</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G131" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H131" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>6</v>
       </c>
@@ -4722,21 +4730,21 @@
         <v>63</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G132" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H132" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>7</v>
       </c>
       <c r="B133" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C133" s="11">
         <v>2014</v>
@@ -4748,16 +4756,16 @@
         <v>63</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G133" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H133" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>8</v>
       </c>
@@ -4774,16 +4782,16 @@
         <v>63</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G134" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H134" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>9</v>
       </c>
@@ -4800,16 +4808,16 @@
         <v>63</v>
       </c>
       <c r="F135" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G135" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H135" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>10</v>
       </c>
@@ -4826,16 +4834,16 @@
         <v>63</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G136" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H136" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>11</v>
       </c>
@@ -4852,16 +4860,16 @@
         <v>63</v>
       </c>
       <c r="F137" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G137" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H137" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>12</v>
       </c>
@@ -4878,16 +4886,16 @@
         <v>63</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G138" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H138" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>13</v>
       </c>
@@ -4904,13 +4912,13 @@
         <v>63</v>
       </c>
       <c r="F139" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H139" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>14</v>
       </c>
@@ -4927,13 +4935,13 @@
         <v>63</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H140" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>15</v>
       </c>
@@ -4950,13 +4958,13 @@
         <v>63</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H141" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="9" t="s">
         <v>0</v>
       </c>
@@ -4973,16 +4981,16 @@
         <v>59</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>1</v>
       </c>
@@ -4999,7 +5007,7 @@
         <v>63</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G144" s="10">
         <v>3</v>
@@ -5008,7 +5016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>2</v>
       </c>
@@ -5025,16 +5033,16 @@
         <v>63</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>3</v>
       </c>
@@ -5051,16 +5059,16 @@
         <v>63</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>4</v>
       </c>
@@ -5077,16 +5085,16 @@
         <v>63</v>
       </c>
       <c r="F147" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H147" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>5</v>
       </c>
@@ -5103,16 +5111,16 @@
         <v>63</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H148" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>6</v>
       </c>
@@ -5129,16 +5137,16 @@
         <v>63</v>
       </c>
       <c r="F149" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H149" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>7</v>
       </c>
@@ -5155,16 +5163,16 @@
         <v>63</v>
       </c>
       <c r="F150" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H150" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>8</v>
       </c>
@@ -5181,16 +5189,16 @@
         <v>63</v>
       </c>
       <c r="F151" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H151" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>9</v>
       </c>
@@ -5207,16 +5215,16 @@
         <v>63</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H152" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>10</v>
       </c>
@@ -5233,16 +5241,16 @@
         <v>63</v>
       </c>
       <c r="F153" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G153" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H153" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>11</v>
       </c>
@@ -5259,16 +5267,16 @@
         <v>63</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G154" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H154" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>12</v>
       </c>
@@ -5285,16 +5293,16 @@
         <v>63</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G155" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H155" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>13</v>
       </c>
@@ -5311,13 +5319,13 @@
         <v>63</v>
       </c>
       <c r="F156" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H156" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>14</v>
       </c>
@@ -5334,15 +5342,15 @@
         <v>63</v>
       </c>
       <c r="F157" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H157" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -5352,7 +5360,7 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
     </row>
-    <row r="160" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="9" t="s">
         <v>0</v>
       </c>
@@ -5369,16 +5377,16 @@
         <v>59</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H160" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="10">
         <v>1</v>
       </c>
@@ -5395,14 +5403,14 @@
         <v>63</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G161" s="10"/>
       <c r="H161" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="10">
         <v>2</v>
       </c>
@@ -5419,14 +5427,14 @@
         <v>63</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G162" s="10"/>
       <c r="H162" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="10">
         <v>3</v>
       </c>
@@ -5443,14 +5451,14 @@
         <v>63</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G163" s="10"/>
       <c r="H163" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="11">
         <v>4</v>
       </c>
@@ -5467,13 +5475,13 @@
         <v>63</v>
       </c>
       <c r="F164" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H164" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="11">
         <v>5</v>
       </c>
@@ -5490,16 +5498,16 @@
         <v>63</v>
       </c>
       <c r="F165" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H165" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="11"/>
     </row>
-    <row r="167" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="9" t="s">
         <v>0</v>
       </c>
@@ -5516,21 +5524,21 @@
         <v>59</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H167" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="11">
         <v>1</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C168" s="10">
         <v>2015</v>
@@ -5542,19 +5550,19 @@
         <v>63</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G168" s="10"/>
       <c r="H168" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="11">
         <v>2</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C169" s="10">
         <v>2015</v>
@@ -5566,14 +5574,14 @@
         <v>63</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G169" s="10"/>
       <c r="H169" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="11">
         <v>3</v>
       </c>
@@ -5590,19 +5598,19 @@
         <v>63</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G170" s="10"/>
       <c r="H170" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="11">
         <v>4</v>
       </c>
       <c r="B171" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C171" s="11">
         <v>2015</v>
@@ -5614,18 +5622,18 @@
         <v>63</v>
       </c>
       <c r="F171" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H171" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="11">
         <v>5</v>
       </c>
       <c r="B172" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C172" s="11">
         <v>2015</v>
@@ -5637,13 +5645,13 @@
         <v>63</v>
       </c>
       <c r="F172" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H172" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="11">
         <v>6</v>
       </c>
@@ -5660,13 +5668,13 @@
         <v>63</v>
       </c>
       <c r="F173" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H173" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="11">
         <v>7</v>
       </c>
@@ -5683,18 +5691,18 @@
         <v>63</v>
       </c>
       <c r="F174" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H174" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="11">
         <v>8</v>
       </c>
       <c r="B175" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C175" s="11">
         <v>2015</v>
@@ -5706,13 +5714,13 @@
         <v>63</v>
       </c>
       <c r="F175" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H175" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="11">
         <v>9</v>
       </c>
@@ -5729,13 +5737,13 @@
         <v>63</v>
       </c>
       <c r="F176" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H176" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="11">
         <v>10</v>
       </c>
@@ -5752,13 +5760,13 @@
         <v>63</v>
       </c>
       <c r="F177" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H177" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="11">
         <v>11</v>
       </c>
@@ -5775,13 +5783,13 @@
         <v>63</v>
       </c>
       <c r="F178" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H178" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="11">
         <v>12</v>
       </c>
@@ -5798,13 +5806,13 @@
         <v>63</v>
       </c>
       <c r="F179" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H179" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="11">
         <v>13</v>
       </c>
@@ -5821,13 +5829,13 @@
         <v>63</v>
       </c>
       <c r="F180" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H180" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="11">
         <v>14</v>
       </c>
@@ -5844,13 +5852,13 @@
         <v>63</v>
       </c>
       <c r="F181" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H181" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="11">
         <v>15</v>
       </c>
@@ -5867,13 +5875,13 @@
         <v>63</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H182" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="11">
         <v>16</v>
       </c>
@@ -5890,13 +5898,13 @@
         <v>63</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H183" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="11">
         <v>17</v>
       </c>
@@ -5913,18 +5921,18 @@
         <v>63</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H184" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="11"/>
     </row>
-    <row r="186" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -5934,7 +5942,7 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
     </row>
-    <row r="187" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="9" t="s">
         <v>0</v>
       </c>
@@ -5951,16 +5959,16 @@
         <v>59</v>
       </c>
       <c r="F187" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H187" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="11">
         <v>1</v>
       </c>
@@ -5977,16 +5985,16 @@
         <v>63</v>
       </c>
       <c r="F188" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G188" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H188" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="11">
         <v>2</v>
       </c>
@@ -6003,16 +6011,16 @@
         <v>63</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G189" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H189" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="11">
         <v>3</v>
       </c>
@@ -6029,16 +6037,16 @@
         <v>63</v>
       </c>
       <c r="F190" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G190" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H190" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="11">
         <v>4</v>
       </c>
@@ -6055,16 +6063,16 @@
         <v>63</v>
       </c>
       <c r="F191" s="11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G191" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H191" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="11">
         <v>5</v>
       </c>
@@ -6081,16 +6089,16 @@
         <v>63</v>
       </c>
       <c r="F192" s="11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G192" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H192" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="11">
         <v>6</v>
       </c>
@@ -6107,16 +6115,16 @@
         <v>63</v>
       </c>
       <c r="F193" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G193" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H193" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="11">
         <v>7</v>
       </c>
@@ -6133,16 +6141,16 @@
         <v>63</v>
       </c>
       <c r="F194" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G194" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H194" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="11">
         <v>8</v>
       </c>
@@ -6159,16 +6167,16 @@
         <v>63</v>
       </c>
       <c r="F195" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G195" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H195" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="11">
         <v>9</v>
       </c>
@@ -6185,13 +6193,13 @@
         <v>63</v>
       </c>
       <c r="F196" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H196" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="11">
         <v>10</v>
       </c>
@@ -6208,16 +6216,16 @@
         <v>63</v>
       </c>
       <c r="F197" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H197" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="11"/>
     </row>
-    <row r="199" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="9" t="s">
         <v>0</v>
       </c>
@@ -6234,16 +6242,16 @@
         <v>59</v>
       </c>
       <c r="F199" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H199" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="10">
         <v>1</v>
       </c>
@@ -6260,7 +6268,7 @@
         <v>63</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G200" s="10">
         <v>3</v>
@@ -6269,7 +6277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="10">
         <v>2</v>
       </c>
@@ -6286,7 +6294,7 @@
         <v>63</v>
       </c>
       <c r="F201" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G201" s="10">
         <v>3</v>
@@ -6295,7 +6303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="10">
         <v>3</v>
       </c>
@@ -6312,7 +6320,7 @@
         <v>63</v>
       </c>
       <c r="F202" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G202" s="10">
         <v>3</v>
@@ -6321,7 +6329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="11">
         <v>4</v>
       </c>
@@ -6338,16 +6346,16 @@
         <v>63</v>
       </c>
       <c r="F203" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H203" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="11">
         <v>5</v>
       </c>
@@ -6364,13 +6372,13 @@
         <v>63</v>
       </c>
       <c r="F204" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H204" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="11">
         <v>6</v>
       </c>
@@ -6387,13 +6395,13 @@
         <v>63</v>
       </c>
       <c r="F205" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H205" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="11">
         <v>7</v>
       </c>
@@ -6410,13 +6418,13 @@
         <v>63</v>
       </c>
       <c r="F206" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H206" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="11">
         <v>8</v>
       </c>
@@ -6433,16 +6441,16 @@
         <v>63</v>
       </c>
       <c r="F207" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H207" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="11"/>
     </row>
-    <row r="209" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="9" t="s">
         <v>0</v>
       </c>
@@ -6459,16 +6467,16 @@
         <v>59</v>
       </c>
       <c r="F209" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H209" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="9">
         <v>1</v>
       </c>
@@ -6485,21 +6493,21 @@
         <v>63</v>
       </c>
       <c r="F210" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G210" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H210" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="9">
         <v>2</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C211" s="10">
         <v>2014</v>
@@ -6511,16 +6519,16 @@
         <v>63</v>
       </c>
       <c r="F211" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G211" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H211" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="9">
         <v>3</v>
       </c>
@@ -6537,16 +6545,16 @@
         <v>63</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G212" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H212" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>4</v>
       </c>
@@ -6563,16 +6571,16 @@
         <v>63</v>
       </c>
       <c r="F213" s="11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G213" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H213" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>5</v>
       </c>
@@ -6589,13 +6597,13 @@
         <v>63</v>
       </c>
       <c r="F214" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H214" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>6</v>
       </c>
@@ -6612,13 +6620,13 @@
         <v>63</v>
       </c>
       <c r="F215" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H215" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>7</v>
       </c>
@@ -6635,13 +6643,13 @@
         <v>63</v>
       </c>
       <c r="F216" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H216" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>8</v>
       </c>
@@ -6658,13 +6666,13 @@
         <v>63</v>
       </c>
       <c r="F217" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H217" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>9</v>
       </c>
@@ -6681,13 +6689,13 @@
         <v>63</v>
       </c>
       <c r="F218" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H218" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>10</v>
       </c>
@@ -6704,13 +6712,13 @@
         <v>63</v>
       </c>
       <c r="F219" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H219" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>11</v>
       </c>
@@ -6727,13 +6735,13 @@
         <v>63</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H220" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>12</v>
       </c>
@@ -6750,13 +6758,13 @@
         <v>63</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H221" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>13</v>
       </c>
@@ -6773,13 +6781,13 @@
         <v>63</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H222" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>14</v>
       </c>
@@ -6796,13 +6804,13 @@
         <v>63</v>
       </c>
       <c r="F223" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H223" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>15</v>
       </c>
@@ -6819,13 +6827,13 @@
         <v>63</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H224" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="9" t="s">
         <v>0</v>
       </c>
@@ -6842,16 +6850,16 @@
         <v>59</v>
       </c>
       <c r="F226" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G226" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H226" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="9">
         <v>1</v>
       </c>
@@ -6868,16 +6876,16 @@
         <v>63</v>
       </c>
       <c r="F227" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H227" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="9">
         <v>2</v>
       </c>
@@ -6894,16 +6902,16 @@
         <v>63</v>
       </c>
       <c r="F228" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G228" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H228" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="9">
         <v>3</v>
       </c>
@@ -6920,16 +6928,16 @@
         <v>63</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G229" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H229" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>4</v>
       </c>
@@ -6946,16 +6954,16 @@
         <v>63</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G230" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H230" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>5</v>
       </c>
@@ -6972,16 +6980,16 @@
         <v>63</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G231" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H231" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>6</v>
       </c>
@@ -6998,16 +7006,16 @@
         <v>63</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G232" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H232" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>7</v>
       </c>
@@ -7024,16 +7032,16 @@
         <v>63</v>
       </c>
       <c r="F233" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H233" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>8</v>
       </c>
@@ -7050,16 +7058,16 @@
         <v>63</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H234" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>9</v>
       </c>
@@ -7076,13 +7084,13 @@
         <v>63</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H235" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>10</v>
       </c>
@@ -7099,13 +7107,13 @@
         <v>63</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H236" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>11</v>
       </c>
@@ -7122,13 +7130,13 @@
         <v>63</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H237" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>12</v>
       </c>
@@ -7145,13 +7153,13 @@
         <v>63</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H238" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>13</v>
       </c>
@@ -7168,13 +7176,13 @@
         <v>63</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H239" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>14</v>
       </c>
@@ -7191,15 +7199,15 @@
         <v>63</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H240" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -7209,7 +7217,7 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
     </row>
-    <row r="243" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="9" t="s">
         <v>0</v>
       </c>
@@ -7226,16 +7234,16 @@
         <v>59</v>
       </c>
       <c r="F243" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G243" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H243" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="10">
         <v>1</v>
       </c>
@@ -7252,14 +7260,14 @@
         <v>63</v>
       </c>
       <c r="F244" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G244" s="10"/>
       <c r="H244" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="10">
         <v>2</v>
       </c>
@@ -7276,14 +7284,14 @@
         <v>63</v>
       </c>
       <c r="F245" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G245" s="10"/>
       <c r="H245" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="10">
         <v>3</v>
       </c>
@@ -7300,14 +7308,14 @@
         <v>63</v>
       </c>
       <c r="F246" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G246" s="10"/>
       <c r="H246" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="11">
         <v>4</v>
       </c>
@@ -7324,13 +7332,13 @@
         <v>63</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H247" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="11">
         <v>5</v>
       </c>
@@ -7347,13 +7355,13 @@
         <v>63</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H248" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="249" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="11">
         <v>6</v>
       </c>
@@ -7370,13 +7378,13 @@
         <v>63</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H249" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="11">
         <v>7</v>
       </c>
@@ -7393,13 +7401,13 @@
         <v>63</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H250" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="11">
         <v>8</v>
       </c>
@@ -7416,13 +7424,13 @@
         <v>63</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H251" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="11">
         <v>9</v>
       </c>
@@ -7439,16 +7447,16 @@
         <v>63</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H252" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="11"/>
     </row>
-    <row r="254" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="9" t="s">
         <v>0</v>
       </c>
@@ -7465,21 +7473,21 @@
         <v>59</v>
       </c>
       <c r="F254" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G254" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H254" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="10">
         <v>1</v>
       </c>
       <c r="B255" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C255" s="10">
         <v>2015</v>
@@ -7491,14 +7499,14 @@
         <v>63</v>
       </c>
       <c r="F255" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G255" s="10"/>
       <c r="H255" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="10">
         <v>2</v>
       </c>
@@ -7515,19 +7523,19 @@
         <v>63</v>
       </c>
       <c r="F256" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G256" s="10"/>
       <c r="H256" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="10">
         <v>3</v>
       </c>
       <c r="B257" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C257" s="10">
         <v>2015</v>
@@ -7539,14 +7547,14 @@
         <v>63</v>
       </c>
       <c r="F257" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G257" s="10"/>
       <c r="H257" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="10">
         <v>4</v>
       </c>
@@ -7563,18 +7571,18 @@
         <v>63</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H258" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="10">
         <v>5</v>
       </c>
       <c r="B259" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C259" s="11">
         <v>2015</v>
@@ -7586,13 +7594,13 @@
         <v>63</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H259" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="10">
         <v>6</v>
       </c>
@@ -7609,13 +7617,13 @@
         <v>63</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H260" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="10">
         <v>7</v>
       </c>
@@ -7632,13 +7640,13 @@
         <v>63</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H261" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="10">
         <v>8</v>
       </c>
@@ -7655,13 +7663,13 @@
         <v>63</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H262" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="10">
         <v>9</v>
       </c>
@@ -7678,13 +7686,13 @@
         <v>63</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H263" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="264" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="10">
         <v>10</v>
       </c>
@@ -7701,18 +7709,18 @@
         <v>63</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H264" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="10">
         <v>11</v>
       </c>
       <c r="B265" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C265" s="11">
         <v>2015</v>
@@ -7724,13 +7732,13 @@
         <v>63</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H265" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="10">
         <v>12</v>
       </c>
@@ -7747,13 +7755,13 @@
         <v>63</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H266" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="10">
         <v>13</v>
       </c>
@@ -7761,10 +7769,10 @@
         <v>79</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="10">
         <v>14</v>
       </c>
@@ -7781,18 +7789,18 @@
         <v>63</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H268" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="10">
         <v>15</v>
       </c>
       <c r="B269" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C269" s="11">
         <v>2015</v>
@@ -7804,13 +7812,13 @@
         <v>63</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H269" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="10">
         <v>16</v>
       </c>
@@ -7827,13 +7835,13 @@
         <v>63</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H270" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="10">
         <v>17</v>
       </c>
@@ -7850,13 +7858,13 @@
         <v>63</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H271" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="10">
         <v>18</v>
       </c>
@@ -7873,13 +7881,13 @@
         <v>63</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H272" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="10">
         <v>19</v>
       </c>
@@ -7896,22 +7904,22 @@
         <v>63</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H273" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C274"/>
       <c r="D274"/>
       <c r="E274"/>
       <c r="F274"/>
       <c r="G274"/>
     </row>
-    <row r="275" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -7921,7 +7929,7 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
     </row>
-    <row r="276" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="9" t="s">
         <v>0</v>
       </c>
@@ -7938,16 +7946,16 @@
         <v>59</v>
       </c>
       <c r="F276" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G276" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H276" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="10">
         <v>1</v>
       </c>
@@ -7964,16 +7972,16 @@
         <v>63</v>
       </c>
       <c r="F277" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G277" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H277" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="10">
         <v>2</v>
       </c>
@@ -7990,16 +7998,16 @@
         <v>63</v>
       </c>
       <c r="F278" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G278" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H278" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="10">
         <v>3</v>
       </c>
@@ -8016,16 +8024,16 @@
         <v>63</v>
       </c>
       <c r="F279" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G279" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H279" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="10">
         <v>4</v>
       </c>
@@ -8042,16 +8050,16 @@
         <v>63</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G280" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H280" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="10">
         <v>5</v>
       </c>
@@ -8068,16 +8076,16 @@
         <v>63</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G281" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H281" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="10">
         <v>6</v>
       </c>
@@ -8094,16 +8102,16 @@
         <v>63</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H282" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="10">
         <v>7</v>
       </c>
@@ -8120,16 +8128,16 @@
         <v>63</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G283" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H283" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="10">
         <v>8</v>
       </c>
@@ -8146,16 +8154,16 @@
         <v>63</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H284" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="10">
         <v>9</v>
       </c>
@@ -8172,13 +8180,13 @@
         <v>63</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H285" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="10">
         <v>10</v>
       </c>
@@ -8195,16 +8203,16 @@
         <v>63</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H286" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="10"/>
     </row>
-    <row r="288" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="9" t="s">
         <v>0</v>
       </c>
@@ -8221,16 +8229,16 @@
         <v>59</v>
       </c>
       <c r="F288" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G288" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H288" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="10">
         <v>1</v>
       </c>
@@ -8247,7 +8255,7 @@
         <v>63</v>
       </c>
       <c r="F289" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G289" s="10">
         <v>3</v>
@@ -8256,7 +8264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="10">
         <v>2</v>
       </c>
@@ -8273,7 +8281,7 @@
         <v>63</v>
       </c>
       <c r="F290" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G290" s="10">
         <v>3</v>
@@ -8282,7 +8290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="10">
         <v>3</v>
       </c>
@@ -8299,16 +8307,16 @@
         <v>63</v>
       </c>
       <c r="F291" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G291" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H291" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="11">
         <v>4</v>
       </c>
@@ -8325,16 +8333,16 @@
         <v>63</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G292" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H292" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="11">
         <v>5</v>
       </c>
@@ -8351,16 +8359,16 @@
         <v>63</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G293" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H293" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="11">
         <v>6</v>
       </c>
@@ -8377,13 +8385,13 @@
         <v>63</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H294" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="11">
         <v>7</v>
       </c>
@@ -8400,13 +8408,13 @@
         <v>63</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H295" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="11">
         <v>8</v>
       </c>
@@ -8423,16 +8431,16 @@
         <v>63</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H296" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="11"/>
     </row>
-    <row r="298" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="9" t="s">
         <v>0</v>
       </c>
@@ -8449,16 +8457,16 @@
         <v>59</v>
       </c>
       <c r="F298" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G298" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H298" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="9">
         <v>1</v>
       </c>
@@ -8475,16 +8483,16 @@
         <v>63</v>
       </c>
       <c r="F299" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G299" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H299" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="9">
         <v>2</v>
       </c>
@@ -8501,16 +8509,16 @@
         <v>63</v>
       </c>
       <c r="F300" s="10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G300" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H300" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="9">
         <v>3</v>
       </c>
@@ -8527,16 +8535,16 @@
         <v>63</v>
       </c>
       <c r="F301" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G301" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H301" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>4</v>
       </c>
@@ -8553,16 +8561,16 @@
         <v>63</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H302" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>5</v>
       </c>
@@ -8579,16 +8587,16 @@
         <v>63</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H303" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>6</v>
       </c>
@@ -8605,21 +8613,21 @@
         <v>63</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G304" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H304" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>7</v>
       </c>
       <c r="B305" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C305" s="11">
         <v>2014</v>
@@ -8631,16 +8639,16 @@
         <v>63</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G305" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H305" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>8</v>
       </c>
@@ -8657,13 +8665,13 @@
         <v>63</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H306" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>9</v>
       </c>
@@ -8680,13 +8688,13 @@
         <v>63</v>
       </c>
       <c r="F307" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H307" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>10</v>
       </c>
@@ -8703,13 +8711,13 @@
         <v>63</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H308" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>11</v>
       </c>
@@ -8726,13 +8734,13 @@
         <v>63</v>
       </c>
       <c r="F309" s="11" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H309" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>12</v>
       </c>
@@ -8749,13 +8757,13 @@
         <v>63</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H310" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>13</v>
       </c>
@@ -8772,13 +8780,13 @@
         <v>63</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H311" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>14</v>
       </c>
@@ -8795,13 +8803,13 @@
         <v>63</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H312" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>15</v>
       </c>
@@ -8818,13 +8826,13 @@
         <v>63</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H313" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="9" t="s">
         <v>0</v>
       </c>
@@ -8841,16 +8849,16 @@
         <v>59</v>
       </c>
       <c r="F315" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G315" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H315" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="9">
         <v>1</v>
       </c>
@@ -8867,16 +8875,16 @@
         <v>63</v>
       </c>
       <c r="F316" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G316" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H316" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="9">
         <v>2</v>
       </c>
@@ -8893,16 +8901,16 @@
         <v>63</v>
       </c>
       <c r="F317" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G317" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H317" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="9">
         <v>3</v>
       </c>
@@ -8919,16 +8927,16 @@
         <v>63</v>
       </c>
       <c r="F318" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G318" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H318" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="9">
         <v>4</v>
       </c>
@@ -8945,16 +8953,16 @@
         <v>63</v>
       </c>
       <c r="F319" s="11" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G319" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H319" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="9">
         <v>5</v>
       </c>
@@ -8971,16 +8979,16 @@
         <v>63</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G320" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H320" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="9">
         <v>6</v>
       </c>
@@ -8997,16 +9005,16 @@
         <v>63</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G321" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H321" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="9">
         <v>7</v>
       </c>
@@ -9023,16 +9031,16 @@
         <v>63</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G322" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H322" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="9">
         <v>8</v>
       </c>
@@ -9049,16 +9057,16 @@
         <v>63</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H323" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="9">
         <v>9</v>
       </c>
@@ -9075,16 +9083,16 @@
         <v>63</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G324" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H324" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="9">
         <v>10</v>
       </c>
@@ -9101,16 +9109,16 @@
         <v>63</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G325" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H325" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="9">
         <v>11</v>
       </c>
@@ -9127,13 +9135,13 @@
         <v>63</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H326" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="9">
         <v>12</v>
       </c>
@@ -9150,13 +9158,13 @@
         <v>63</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H327" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="9">
         <v>13</v>
       </c>
@@ -9173,13 +9181,13 @@
         <v>63</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H328" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="9">
         <v>14</v>
       </c>
@@ -9196,18 +9204,18 @@
         <v>63</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H329" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="9">
         <v>15</v>
       </c>
       <c r="B330" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C330" s="11">
         <v>2012</v>
@@ -9219,21 +9227,21 @@
         <v>63</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G330" s="11">
         <v>3</v>
       </c>
       <c r="H330" s="11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="331" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="9">
         <v>16</v>
       </c>
       <c r="B331" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C331" s="11">
         <v>2011</v>
@@ -9245,21 +9253,21 @@
         <v>63</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G331" s="11">
         <v>3</v>
       </c>
       <c r="H331" s="11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="332" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="9">
         <v>17</v>
       </c>
       <c r="B332" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C332" s="11">
         <v>2012</v>
@@ -9271,13 +9279,13 @@
         <v>63</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G332" s="11">
         <v>2</v>
       </c>
       <c r="H332" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -9305,16 +9313,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F383"/>
-  <sheetFormatPr defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="5" customWidth="1"/>
-    <col min="4" max="6" width="19.42578125" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="3.359375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.38671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.609375" style="5" customWidth="1"/>
+    <col min="4" max="6" width="19.37109375" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="9.14453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="22">
         <v>45717</v>
       </c>
@@ -9326,9 +9334,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -9336,7 +9344,7 @@
       <c r="E2" s="23"/>
       <c r="F2" s="23"/>
     </row>
-    <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -9344,7 +9352,7 @@
       <c r="E3" s="24"/>
       <c r="F3" s="24"/>
     </row>
-    <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
         <v>57</v>
       </c>
@@ -9354,7 +9362,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
     </row>
-    <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -9365,20 +9373,20 @@
         <v>61</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>169</v>
-      </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -9389,7 +9397,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>2</v>
       </c>
@@ -9400,7 +9408,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>3</v>
       </c>
@@ -9411,7 +9419,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>4</v>
       </c>
@@ -9422,7 +9430,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>5</v>
       </c>
@@ -9433,7 +9441,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>6</v>
       </c>
@@ -9444,13 +9452,13 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>1</v>
       </c>
@@ -9461,7 +9469,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>2</v>
       </c>
@@ -9472,7 +9480,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>3</v>
       </c>
@@ -9483,7 +9491,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>4</v>
       </c>
@@ -9494,7 +9502,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>5</v>
       </c>
@@ -9505,7 +9513,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>6</v>
       </c>
@@ -9516,13 +9524,13 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>1</v>
       </c>
@@ -9533,7 +9541,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>2</v>
       </c>
@@ -9544,7 +9552,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>3</v>
       </c>
@@ -9555,7 +9563,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -9566,7 +9574,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>5</v>
       </c>
@@ -9577,7 +9585,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>6</v>
       </c>
@@ -9588,10 +9596,10 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>0</v>
       </c>
@@ -9605,13 +9613,13 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
       <c r="B29" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -9622,7 +9630,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -9633,7 +9641,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -9644,7 +9652,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -9655,7 +9663,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>6</v>
       </c>
@@ -9666,12 +9674,12 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -9682,7 +9690,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>2</v>
       </c>
@@ -9693,7 +9701,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>3</v>
       </c>
@@ -9704,7 +9712,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -9715,7 +9723,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>5</v>
       </c>
@@ -9726,7 +9734,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -9737,12 +9745,12 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>1</v>
       </c>
@@ -9753,7 +9761,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>2</v>
       </c>
@@ -9764,7 +9772,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>3</v>
       </c>
@@ -9775,7 +9783,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>4</v>
       </c>
@@ -9786,7 +9794,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -9797,7 +9805,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -9808,12 +9816,12 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>1</v>
       </c>
@@ -9824,7 +9832,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>2</v>
       </c>
@@ -9835,7 +9843,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>3</v>
       </c>
@@ -9846,7 +9854,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>4</v>
       </c>
@@ -9857,7 +9865,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>5</v>
       </c>
@@ -9868,7 +9876,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9879,12 +9887,12 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>1</v>
       </c>
@@ -9895,7 +9903,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>2</v>
       </c>
@@ -9906,7 +9914,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>3</v>
       </c>
@@ -9917,7 +9925,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>4</v>
       </c>
@@ -9928,7 +9936,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>5</v>
       </c>
@@ -9939,7 +9947,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -9950,7 +9958,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="18" t="s">
         <v>106</v>
       </c>
@@ -9960,7 +9968,7 @@
       <c r="E65" s="18"/>
       <c r="F65" s="18"/>
     </row>
-    <row r="66" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>0</v>
       </c>
@@ -9974,23 +9982,23 @@
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
     </row>
-    <row r="67" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3"/>
       <c r="B67" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
     </row>
-    <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <v>1</v>
       </c>
       <c r="B68" s="3"/>
     </row>
-    <row r="69" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <v>2</v>
       </c>
@@ -10001,7 +10009,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <v>3</v>
       </c>
@@ -10012,7 +10020,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <v>4</v>
       </c>
@@ -10023,7 +10031,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5">
         <v>5</v>
       </c>
@@ -10034,18 +10042,18 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5"/>
       <c r="B74" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5">
         <v>1</v>
       </c>
@@ -10056,7 +10064,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5">
         <v>2</v>
       </c>
@@ -10067,7 +10075,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <v>3</v>
       </c>
@@ -10078,7 +10086,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <v>4</v>
       </c>
@@ -10089,7 +10097,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <v>5</v>
       </c>
@@ -10100,7 +10108,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <v>6</v>
       </c>
@@ -10111,10 +10119,10 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>0</v>
       </c>
@@ -10128,13 +10136,13 @@
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
     </row>
-    <row r="83" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5"/>
       <c r="B83" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5">
         <v>1</v>
       </c>
@@ -10145,7 +10153,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5">
         <v>2</v>
       </c>
@@ -10156,7 +10164,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5">
         <v>3</v>
       </c>
@@ -10167,7 +10175,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5">
         <v>4</v>
       </c>
@@ -10178,7 +10186,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="5">
         <v>5</v>
       </c>
@@ -10189,7 +10197,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5">
         <v>6</v>
       </c>
@@ -10200,13 +10208,13 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5"/>
       <c r="B90" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="5">
         <v>1</v>
       </c>
@@ -10217,7 +10225,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5">
         <v>2</v>
       </c>
@@ -10228,7 +10236,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5">
         <v>3</v>
       </c>
@@ -10239,7 +10247,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5">
         <v>4</v>
       </c>
@@ -10250,7 +10258,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5">
         <v>5</v>
       </c>
@@ -10261,7 +10269,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5">
         <v>6</v>
       </c>
@@ -10272,16 +10280,16 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5"/>
       <c r="B98" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5">
         <v>1</v>
       </c>
@@ -10292,7 +10300,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5">
         <v>2</v>
       </c>
@@ -10303,7 +10311,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5">
         <v>3</v>
       </c>
@@ -10314,7 +10322,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5">
         <v>4</v>
       </c>
@@ -10325,7 +10333,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5">
         <v>5</v>
       </c>
@@ -10336,7 +10344,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5">
         <v>6</v>
       </c>
@@ -10347,18 +10355,18 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5"/>
       <c r="B105" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5">
         <v>2</v>
       </c>
@@ -10369,7 +10377,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5">
         <v>3</v>
       </c>
@@ -10380,7 +10388,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5">
         <v>4</v>
       </c>
@@ -10391,7 +10399,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5">
         <v>5</v>
       </c>
@@ -10402,21 +10410,21 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5"/>
       <c r="B113" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5">
         <v>1</v>
       </c>
@@ -10427,7 +10435,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5">
         <v>2</v>
       </c>
@@ -10438,7 +10446,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5">
         <v>3</v>
       </c>
@@ -10449,7 +10457,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5">
         <v>4</v>
       </c>
@@ -10460,7 +10468,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5">
         <v>5</v>
       </c>
@@ -10471,7 +10479,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5">
         <v>6</v>
       </c>
@@ -10482,10 +10490,10 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="18" t="s">
         <v>106</v>
       </c>
@@ -10495,7 +10503,7 @@
       <c r="E121" s="18"/>
       <c r="F121" s="18"/>
     </row>
-    <row r="122" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>0</v>
       </c>
@@ -10509,13 +10517,13 @@
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
     </row>
-    <row r="123" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5"/>
       <c r="B123" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5">
         <v>1</v>
       </c>
@@ -10526,7 +10534,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5">
         <v>2</v>
       </c>
@@ -10537,7 +10545,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5">
         <v>3</v>
       </c>
@@ -10548,7 +10556,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5">
         <v>4</v>
       </c>
@@ -10559,7 +10567,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5">
         <v>5</v>
       </c>
@@ -10570,7 +10578,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5">
         <v>6</v>
       </c>
@@ -10581,13 +10589,13 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5"/>
       <c r="B130" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5">
         <v>1</v>
       </c>
@@ -10598,7 +10606,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5">
         <v>2</v>
       </c>
@@ -10609,7 +10617,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="5">
         <v>3</v>
       </c>
@@ -10620,7 +10628,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="5">
         <v>4</v>
       </c>
@@ -10631,7 +10639,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="5">
         <v>5</v>
       </c>
@@ -10642,7 +10650,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="5">
         <v>6</v>
       </c>
@@ -10653,13 +10661,13 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="5"/>
       <c r="B137" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="5">
         <v>1</v>
       </c>
@@ -10670,7 +10678,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="5">
         <v>2</v>
       </c>
@@ -10681,7 +10689,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="5">
         <v>3</v>
       </c>
@@ -10692,7 +10700,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="5">
         <v>4</v>
       </c>
@@ -10703,7 +10711,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="5">
         <v>5</v>
       </c>
@@ -10714,7 +10722,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="5">
         <v>6</v>
       </c>
@@ -10725,10 +10733,10 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>0</v>
       </c>
@@ -10742,13 +10750,13 @@
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
     </row>
-    <row r="146" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="5"/>
       <c r="B146" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>2</v>
       </c>
@@ -10759,7 +10767,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>3</v>
       </c>
@@ -10770,7 +10778,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>4</v>
       </c>
@@ -10781,7 +10789,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>5</v>
       </c>
@@ -10792,7 +10800,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>6</v>
       </c>
@@ -10803,12 +10811,12 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B152" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>1</v>
       </c>
@@ -10819,7 +10827,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>2</v>
       </c>
@@ -10830,7 +10838,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>3</v>
       </c>
@@ -10841,7 +10849,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>4</v>
       </c>
@@ -10852,7 +10860,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>5</v>
       </c>
@@ -10863,7 +10871,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>6</v>
       </c>
@@ -10874,12 +10882,12 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B159" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>1</v>
       </c>
@@ -10890,7 +10898,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>2</v>
       </c>
@@ -10901,7 +10909,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>3</v>
       </c>
@@ -10912,7 +10920,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>4</v>
       </c>
@@ -10923,7 +10931,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>5</v>
       </c>
@@ -10934,7 +10942,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>6</v>
       </c>
@@ -10945,12 +10953,12 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B166" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>1</v>
       </c>
@@ -10961,7 +10969,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>2</v>
       </c>
@@ -10972,7 +10980,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>3</v>
       </c>
@@ -10983,7 +10991,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>4</v>
       </c>
@@ -10994,7 +11002,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>5</v>
       </c>
@@ -11005,7 +11013,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>6</v>
       </c>
@@ -11016,12 +11024,12 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B173" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>1</v>
       </c>
@@ -11032,7 +11040,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>2</v>
       </c>
@@ -11043,7 +11051,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>3</v>
       </c>
@@ -11054,7 +11062,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>4</v>
       </c>
@@ -11065,7 +11073,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>5</v>
       </c>
@@ -11076,7 +11084,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>6</v>
       </c>
@@ -11087,9 +11095,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B181" s="18"/>
       <c r="C181" s="18"/>
@@ -11097,7 +11105,7 @@
       <c r="E181" s="18"/>
       <c r="F181" s="18"/>
     </row>
-    <row r="182" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
         <v>0</v>
       </c>
@@ -11111,15 +11119,15 @@
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
     </row>
-    <row r="183" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="5">
         <v>1</v>
       </c>
@@ -11130,7 +11138,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="5">
         <v>2</v>
       </c>
@@ -11141,7 +11149,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="5">
         <v>3</v>
       </c>
@@ -11152,7 +11160,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="5">
         <v>4</v>
       </c>
@@ -11163,7 +11171,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="5">
         <v>5</v>
       </c>
@@ -11174,15 +11182,15 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
         <v>0</v>
       </c>
@@ -11196,13 +11204,13 @@
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
     </row>
-    <row r="192" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="5"/>
       <c r="B192" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="5">
         <v>1</v>
       </c>
@@ -11213,7 +11221,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="5">
         <v>2</v>
       </c>
@@ -11224,7 +11232,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="5">
         <v>3</v>
       </c>
@@ -11235,7 +11243,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="5">
         <v>4</v>
       </c>
@@ -11246,7 +11254,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="5">
         <v>5</v>
       </c>
@@ -11257,29 +11265,29 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="5"/>
       <c r="B199" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="5">
         <v>1</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C200" s="5">
         <v>2015</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="5">
         <v>2</v>
       </c>
@@ -11290,7 +11298,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="5">
         <v>3</v>
       </c>
@@ -11301,7 +11309,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="5">
         <v>4</v>
       </c>
@@ -11312,7 +11320,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="5">
         <v>5</v>
       </c>
@@ -11323,7 +11331,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="5">
         <v>6</v>
       </c>
@@ -11334,13 +11342,13 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="5"/>
       <c r="B206" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="5">
         <v>1</v>
       </c>
@@ -11351,7 +11359,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="5">
         <v>2</v>
       </c>
@@ -11362,29 +11370,29 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="5">
         <v>3</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C209" s="5">
         <v>2015</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="5">
         <v>4</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C210" s="5">
         <v>2015</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="5">
         <v>5</v>
       </c>
@@ -11395,23 +11403,23 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="5">
         <v>6</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C212" s="5">
         <v>2015</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="5"/>
     </row>
-    <row r="214" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B214" s="18"/>
       <c r="C214" s="18"/>
@@ -11419,7 +11427,7 @@
       <c r="E214" s="18"/>
       <c r="F214" s="18"/>
     </row>
-    <row r="215" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
         <v>0</v>
       </c>
@@ -11433,15 +11441,15 @@
       <c r="E215" s="4"/>
       <c r="F215" s="4"/>
     </row>
-    <row r="216" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="5">
         <v>1</v>
       </c>
@@ -11452,7 +11460,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="5">
         <v>2</v>
       </c>
@@ -11463,7 +11471,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="5">
         <v>3</v>
       </c>
@@ -11474,7 +11482,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="5">
         <v>4</v>
       </c>
@@ -11485,7 +11493,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="221" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="5">
         <v>5</v>
       </c>
@@ -11496,7 +11504,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="5">
         <v>6</v>
       </c>
@@ -11507,13 +11515,13 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="223" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="5"/>
       <c r="B223" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="5">
         <v>1</v>
       </c>
@@ -11524,7 +11532,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="225" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="5">
         <v>2</v>
       </c>
@@ -11535,7 +11543,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="226" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="5">
         <v>3</v>
       </c>
@@ -11546,7 +11554,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="5">
         <v>4</v>
       </c>
@@ -11557,7 +11565,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="5">
         <v>5</v>
       </c>
@@ -11568,7 +11576,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="229" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="5">
         <v>6</v>
       </c>
@@ -11579,13 +11587,13 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="230" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="5"/>
       <c r="B230" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="5">
         <v>1</v>
       </c>
@@ -11596,7 +11604,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="5">
         <v>2</v>
       </c>
@@ -11607,7 +11615,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="5">
         <v>3</v>
       </c>
@@ -11618,7 +11626,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="5">
         <v>4</v>
       </c>
@@ -11629,7 +11637,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="235" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="5">
         <v>5</v>
       </c>
@@ -11640,7 +11648,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="236" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="5">
         <v>6</v>
       </c>
@@ -11651,10 +11659,10 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="5"/>
     </row>
-    <row r="238" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
         <v>0</v>
       </c>
@@ -11668,13 +11676,13 @@
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
     </row>
-    <row r="239" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="5"/>
       <c r="B239" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>2</v>
       </c>
@@ -11685,7 +11693,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>3</v>
       </c>
@@ -11696,7 +11704,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>4</v>
       </c>
@@ -11707,7 +11715,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>5</v>
       </c>
@@ -11718,7 +11726,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>6</v>
       </c>
@@ -11729,12 +11737,12 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B245" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>1</v>
       </c>
@@ -11745,7 +11753,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>2</v>
       </c>
@@ -11756,7 +11764,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>3</v>
       </c>
@@ -11767,7 +11775,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>4</v>
       </c>
@@ -11778,7 +11786,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>5</v>
       </c>
@@ -11789,7 +11797,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>6</v>
       </c>
@@ -11800,12 +11808,12 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B252" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>1</v>
       </c>
@@ -11816,7 +11824,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>2</v>
       </c>
@@ -11827,7 +11835,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>3</v>
       </c>
@@ -11838,7 +11846,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>4</v>
       </c>
@@ -11849,7 +11857,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>5</v>
       </c>
@@ -11860,7 +11868,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>6</v>
       </c>
@@ -11871,12 +11879,12 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B259" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>1</v>
       </c>
@@ -11887,7 +11895,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>2</v>
       </c>
@@ -11898,7 +11906,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>3</v>
       </c>
@@ -11909,7 +11917,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>4</v>
       </c>
@@ -11920,7 +11928,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>5</v>
       </c>
@@ -11931,7 +11939,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>6</v>
       </c>
@@ -11942,12 +11950,12 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B266" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>1</v>
       </c>
@@ -11958,7 +11966,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>2</v>
       </c>
@@ -11969,7 +11977,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>3</v>
       </c>
@@ -11980,7 +11988,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>4</v>
       </c>
@@ -11991,7 +11999,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>5</v>
       </c>
@@ -12002,7 +12010,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>6</v>
       </c>
@@ -12013,9 +12021,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="274" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B274" s="18"/>
       <c r="C274" s="18"/>
@@ -12023,7 +12031,7 @@
       <c r="E274" s="18"/>
       <c r="F274" s="18"/>
     </row>
-    <row r="275" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="3" t="s">
         <v>0</v>
       </c>
@@ -12037,18 +12045,18 @@
       <c r="E275" s="4"/>
       <c r="F275" s="4"/>
     </row>
-    <row r="276" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="6"/>
       <c r="B276" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="5">
         <v>2</v>
       </c>
@@ -12059,7 +12067,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="279" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="5">
         <v>3</v>
       </c>
@@ -12070,7 +12078,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="280" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="5">
         <v>4</v>
       </c>
@@ -12081,23 +12089,23 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="281" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="283" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="5"/>
       <c r="B283" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="5">
         <v>1</v>
       </c>
@@ -12108,18 +12116,18 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="285" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="5">
         <v>2</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C285" s="5">
         <v>2015</v>
       </c>
     </row>
-    <row r="286" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="5">
         <v>3</v>
       </c>
@@ -12130,7 +12138,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="287" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="5">
         <v>4</v>
       </c>
@@ -12141,7 +12149,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="288" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="5">
         <v>5</v>
       </c>
@@ -12152,7 +12160,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="5">
         <v>6</v>
       </c>
@@ -12163,10 +12171,10 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="290" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="5"/>
     </row>
-    <row r="291" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="3" t="s">
         <v>0</v>
       </c>
@@ -12180,13 +12188,13 @@
       <c r="E291" s="4"/>
       <c r="F291" s="4"/>
     </row>
-    <row r="292" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="5"/>
       <c r="B292" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="5">
         <v>1</v>
       </c>
@@ -12197,12 +12205,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="294" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="5">
         <v>3</v>
       </c>
@@ -12213,7 +12221,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="296" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="5">
         <v>4</v>
       </c>
@@ -12224,12 +12232,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="297" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="5">
         <v>6</v>
       </c>
@@ -12240,18 +12248,18 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="299" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="5"/>
       <c r="B299" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="5">
         <v>2</v>
       </c>
@@ -12262,7 +12270,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="302" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="5">
         <v>3</v>
       </c>
@@ -12273,7 +12281,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="303" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="5">
         <v>4</v>
       </c>
@@ -12284,23 +12292,23 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="304" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="305" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="5"/>
       <c r="B306" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="5">
         <v>1</v>
       </c>
@@ -12311,7 +12319,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="308" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="5">
         <v>2</v>
       </c>
@@ -12322,7 +12330,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="5">
         <v>3</v>
       </c>
@@ -12333,18 +12341,18 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="310" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="5">
         <v>4</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C310" s="5">
         <v>2015</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="5">
         <v>5</v>
       </c>
@@ -12355,24 +12363,24 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="312" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="5">
         <v>6</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C312" s="5">
         <v>2015</v>
       </c>
     </row>
-    <row r="313" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="5"/>
       <c r="B313" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="5">
         <v>1</v>
       </c>
@@ -12383,40 +12391,40 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="315" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="5">
         <v>2</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C315" s="5">
         <v>2015</v>
       </c>
     </row>
-    <row r="316" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="5">
         <v>3</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C316" s="5">
         <v>2015</v>
       </c>
     </row>
-    <row r="317" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="5">
         <v>4</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C317" s="5">
         <v>2015</v>
       </c>
     </row>
-    <row r="318" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="5">
         <v>5</v>
       </c>
@@ -12427,7 +12435,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="319" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="5">
         <v>6</v>
       </c>
@@ -12438,15 +12446,15 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="320" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C320" s="1"/>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
     </row>
-    <row r="321" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B321" s="18"/>
       <c r="C321" s="18"/>
@@ -12454,7 +12462,7 @@
       <c r="E321" s="18"/>
       <c r="F321" s="18"/>
     </row>
-    <row r="322" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="3" t="s">
         <v>0</v>
       </c>
@@ -12468,13 +12476,13 @@
       <c r="E322" s="4"/>
       <c r="F322" s="4"/>
     </row>
-    <row r="323" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="6"/>
       <c r="B323" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="5">
         <v>1</v>
       </c>
@@ -12485,7 +12493,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="325" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="5">
         <v>2</v>
       </c>
@@ -12496,7 +12504,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="326" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="5">
         <v>3</v>
       </c>
@@ -12507,7 +12515,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="327" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="5">
         <v>4</v>
       </c>
@@ -12518,7 +12526,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="328" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="5">
         <v>5</v>
       </c>
@@ -12529,7 +12537,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="329" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="5">
         <v>6</v>
       </c>
@@ -12540,13 +12548,13 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="330" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="5"/>
       <c r="B330" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="331" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="5">
         <v>1</v>
       </c>
@@ -12557,7 +12565,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="332" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="5">
         <v>2</v>
       </c>
@@ -12568,7 +12576,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="333" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="5">
         <v>3</v>
       </c>
@@ -12579,7 +12587,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="334" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="5">
         <v>4</v>
       </c>
@@ -12590,7 +12598,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="335" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="5">
         <v>5</v>
       </c>
@@ -12601,7 +12609,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="336" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="5">
         <v>6</v>
       </c>
@@ -12612,13 +12620,13 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="337" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="5"/>
       <c r="B337" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="5">
         <v>1</v>
       </c>
@@ -12629,7 +12637,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="339" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="5">
         <v>2</v>
       </c>
@@ -12640,7 +12648,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="340" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="5">
         <v>3</v>
       </c>
@@ -12651,7 +12659,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="341" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="5">
         <v>4</v>
       </c>
@@ -12662,7 +12670,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="342" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="5">
         <v>5</v>
       </c>
@@ -12673,7 +12681,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="343" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="5">
         <v>6</v>
       </c>
@@ -12684,10 +12692,10 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="344" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="5"/>
     </row>
-    <row r="345" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="3" t="s">
         <v>0</v>
       </c>
@@ -12701,13 +12709,13 @@
       <c r="E345" s="4"/>
       <c r="F345" s="4"/>
     </row>
-    <row r="346" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="5"/>
       <c r="B346" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="347" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>2</v>
       </c>
@@ -12718,7 +12726,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="348" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>3</v>
       </c>
@@ -12729,7 +12737,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="349" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>4</v>
       </c>
@@ -12740,7 +12748,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="350" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>5</v>
       </c>
@@ -12751,7 +12759,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="351" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>6</v>
       </c>
@@ -12762,12 +12770,12 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="352" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B352" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>1</v>
       </c>
@@ -12778,7 +12786,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>2</v>
       </c>
@@ -12789,7 +12797,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>3</v>
       </c>
@@ -12800,7 +12808,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>4</v>
       </c>
@@ -12811,7 +12819,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>5</v>
       </c>
@@ -12822,7 +12830,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>6</v>
       </c>
@@ -12833,12 +12841,12 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B359" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>1</v>
       </c>
@@ -12849,7 +12857,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>2</v>
       </c>
@@ -12860,7 +12868,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>3</v>
       </c>
@@ -12871,7 +12879,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>4</v>
       </c>
@@ -12882,7 +12890,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>5</v>
       </c>
@@ -12893,7 +12901,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>6</v>
       </c>
@@ -12904,12 +12912,12 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B366" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>1</v>
       </c>
@@ -12920,7 +12928,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>2</v>
       </c>
@@ -12931,7 +12939,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="369" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>3</v>
       </c>
@@ -12942,7 +12950,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="370" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>4</v>
       </c>
@@ -12953,7 +12961,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="371" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>5</v>
       </c>
@@ -12964,7 +12972,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>6</v>
       </c>
@@ -12975,12 +12983,12 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="373" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B373" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>1</v>
       </c>
@@ -12991,7 +12999,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>2</v>
       </c>
@@ -13002,7 +13010,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="376" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>3</v>
       </c>
@@ -13013,7 +13021,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="377" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>4</v>
       </c>
@@ -13024,7 +13032,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="378" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>5</v>
       </c>
@@ -13035,7 +13043,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>6</v>
       </c>
@@ -13046,51 +13054,51 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B380" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="381" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>2</v>
       </c>
       <c r="B381" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C381" s="5">
         <v>2012</v>
       </c>
       <c r="F381" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="382" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>3</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C382" s="5">
         <v>2011</v>
       </c>
       <c r="F382" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="383" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>4</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C383" s="5">
         <v>2012</v>
       </c>
       <c r="F383" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
